--- a/pacjenci/OLEKSANDR ZAKREVSKYI.xlsx
+++ b/pacjenci/OLEKSANDR ZAKREVSKYI.xlsx
@@ -483,10 +483,14 @@
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktywna choroba</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -523,7 +527,11 @@
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>Do oceny</t>
@@ -563,7 +571,11 @@
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Do oceny</t>
@@ -603,7 +615,11 @@
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>Do oceny</t>
@@ -643,7 +659,11 @@
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>Do oceny</t>

--- a/pacjenci/OLEKSANDR ZAKREVSKYI.xlsx
+++ b/pacjenci/OLEKSANDR ZAKREVSKYI.xlsx
@@ -413,279 +413,209 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>12.05.2022</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak z komórek B. Ocena rozległości przed leczeniem.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po  60min od podania 18F-FDG. Glikemia: 99mg%</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Rozległa masa miękkotkankowa w środpiersiu w części środkowej i po stronie prawej wielkości 134x93mm, z obszarami rozpadu, SUV max 4,8. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Płyn w jamie opłucnowej prawej o grubości warstwy 34mm. Zwiększona ilość płynu w osierdziu. Niewielkie zmiany niedodmowe w płacie środkowym płuca prawego.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym.   Wartości referencyjne: MBPS SUVmax do 1,6 Prawy płat wątroby SUVmax do 2,4.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie procesu chłoniakowego w śródpiersiu. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>4.8</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>28.06.2022</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak z komórek B. Ocena efektów leczenia po 4 cyklach chemioterapii.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 102mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Polipowate zgrubienie błony śluzowej w sitowiu po stronie prawej.  Klatka piersiowa i śródpiersie: Masa miękkotkankowa w śródpiersiu przednim i środkowym, pośrodkowo i po stronie prawej, wielkości ok.  89x46x98mm, z obszarami rozpadu, SUV max do 3,4. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zwiększona ilość płynu w worku osierdziowym, o szerokości płaszcza - do 12mm, a nadprzeponowo do 28mm. Obwodowe zmiany włókniste w płacie górnym płuca prawego. Niewielkie zmiany włókniste w segm. 5 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Pobudzenie metaboliczne w układzie kostnym- związane ze stosowanym leczeniem?. Spłycenie fizjologicznych krzywizn kręgosłupa. Dyskopatia na poziomie L5/S1. Os sacrum arcuatum.   Wartości referencyjne: MBPS SUVmax do 1,8; Prawy płat wątroby SUVmax do 3,1.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono dobrą odpowiedź metaboliczną i radiologiczną na stosowane leczenie. Masa resztkowa w śródpiersiu - do dalszej kontroli.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>3.4</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>12.09.2022</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak z komórek B. Ocena efektów leczenia po 6 cyklach chemioterapii.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 63 min od podania 18F-FDG. Glikemia: 102mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Aktywność metaboliczna w prawym fałdzie nalewkowo-nagłośniowym, SUV max 5,3- do ew. kontroli laryngologicznej.   Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Polipowate zgrubienie błony śluzowej w sitowiu po stronie prawej.  Klatka piersiowa i śródpiersie: Masa miękkotkankowa w śródpiersiu przednim i środkowym, pośrodkowo i po stronie prawej, wielkości ok. 62x29x50mm, z obszarami rozpadu, SUV max do 3,7. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zwiększona ilość płynu w worku osierdziowym, o szerokości płaszcza - do 12 mm nadprzeponowo. Obwodowe zmiany włókniste w płacie górnym płuca prawego. Niewielkie zmiany włókniste w segm. 5 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Pobudzenie metaboliczne w układzie kostnym- związane ze stosowanym leczeniem?. Spłycenie fizjologicznych krzywizn kręgosłupa. Dyskopatia na poziomie L5/S1. Os sacrum arcuatum.   Wartości referencyjne: MBPS SUVmax do 1,6; Prawy płat wątroby SUVmax do 2,5.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywność metaboliczną w  prawym fałdzie nalewkowo-nagłośniowym- do ew. kontroli laryngologicznej.    Poza tym jak z badaniu z dnia 28.06.2022 masa resztkowa w śródpiersiu - do dalszej kontroli.   Ponadto jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>5.3</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>06.02.2023</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>Chłoniak z komórek B. Ocena remisji choroby 3 miesiące po zakończeniu IFRT.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58min od podania 18F-FDG. Glikemia: 92mg%.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Polipowate zgrubienie błony śluzowej w sitowiu po stronie prawej. Węzeł chłonny przedziału 3 po stronie prawej wielkości 10mm, SUV max 1,5 [IM 80].  Klatka piersiowa i śródpiersie: Masa miękkotkankowa w śródpiersiu przednim i środkowym, pośrodkowo i po stronie prawej, wielkości ok. 58x26x50mm, z hyperdensyjnymi obszarami, głównie nieaktywna metabolicznie, z wartościami SUV max do 2,5 (w okolicach zmian hyperdensyjnych). Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zwiększona ilość płynu w worku osierdziowym, o szerokości płaszcza - do 11mm. Obwodowe zmiany włókniste w płacie górnym płuca prawego. Drobne zmiany włókniste w segm. 5 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Pobudzenie metaboliczne w układzie kostnym- związane ze stosowanym leczeniem?. Spłycenie fizjologicznych krzywizn kręgosłupa. Łukowato kyfotyczne ustawienie kręgosłupa szyjnego. Niewielka prawowypukła skolioza kręgosłupa piersiowego, z rotacją kręgów. Dyskopatia na poziomie L5/S1. Os sacrum arcuatum. Ok. 4mm wyspy kostne w lewej kości kulszowej i w głowie lewej kości udowej. Drobne obwodowe torbielki i wyspa kostna w głowie prawej kosci udowej.  Inne: Miejednoznaczne mierne pobudzenie metaboliczne w mięśniu czworobocznym lędźwi po stronie lewej, SUV max 2,2 - do kontroli.    Wartości referencyjne: MBPS SUVmax do 1,2 Prawy płat wątroby SUVmax do 2,2.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność masy resztkowej w śródpiersiu, głównie nieaktywnej metabolicznie, ogniskowo miernie pobudzonej metabolicznie (w okolicach zmian hyperdensyjnych)- do dalszej kontroli.   Ponadto jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>2.5</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>16.05.2023</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>Chłoniak z komórek B. Po zakończeniu IFRT. Ocena remisji choroby</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57min od podania 18F-FDG. Glikemia: 106mg%.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Polipowate zgrubienie błony śluzowej w sitowiu po stronie prawej.   Klatka piersiowa i śródpiersie: Masa miękkotkankowa w śródpiersiu przednim i środkowym, pośrodkowo i po stronie prawej, wielkości ok. 46x13x41mm, z hyperdensyjnymi obszarami, głównie nieaktywna metabolicznie, z wartościami SUV max do 2,9 (w okolicach zmian hyperdensyjnych). Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zwiększona ilość płynu w worku osierdziowym, o szerokości płaszcza - do 11mm nadprzeponowo. Obwodowe zmiany włókniste w płacie górnym płuca prawego. Drobne zmiany włókniste w segm. 5 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Pobudzenie metaboliczne w układzie kostnym- związane ze stosowanym leczeniem?. Spłycenie fizjologicznych krzywizn kręgosłupa. Łukowato kyfotyczne ustawienie kręgosłupa szyjnego. Niewielka prawowypukła skolioza kręgosłupa piersiowego, z rotacją kręgów. Dyskopatia na poziomie L5/S1. Os sacrum arcuatum. Ok. 4mm wyspy kostne w lewej kości kulszowej i w głowie lewej kości udowej. Drobne obwodowe torbielki i wyspa kostna w głowie prawej kości udowej.  Inne: Zwiększony metabolizm FDG w tkance brunatnej szyi i KLP.   Wartości referencyjne: MBPS SUVmax do 1,8 Prawy płat wątroby SUVmax do 2,9.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono jak w badaniu poprzednim obecność masy resztkowej w śródpiersiu, głównie nieaktywnej metabolicznie, ogniskowo miernie pobudzonej metabolicznie (w okolicach zmian hyperdensyjnych)- do dalszej kontroli.   Ponadto jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>2.9</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/OLEKSANDR ZAKREVSKYI.xlsx
+++ b/pacjenci/OLEKSANDR ZAKREVSKYI.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po  60min od podania 18F-FDG. Glikemia: 99mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Rozległa masa miękkotkankowa w środpiersiu w części środkowej i po stronie prawej wielkości 134x93mm, z obszarami rozpadu, SUV max 4,8. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Płyn w jamie opłucnowej prawej o grubości warstwy 34mm. Zwiększona ilość płynu w osierdziu. Niewielkie zmiany niedodmowe w płacie środkowym płuca prawego.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym.   Wartości referencyjne: MBPS SUVmax do 1,6 Prawy płat wątroby SUVmax do 2,4.</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Rozległa masa miękkotkankowa w środpiersiu w części środkowej i po stronie prawej wielkości 134x93mm, z obszarami rozpadu, SUV max 4,8. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Płyn w jamie opłucnowej prawej o grubości warstwy 34mm. Zwiększona ilość płynu w osierdziu. Niewielkie zmiany niedodmowe w płacie środkowym płuca prawego.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie procesu chłoniakowego w śródpiersiu. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>4.8</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  57min od podania 18F-FDG. Glikemia: 102mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Polipowate zgrubienie błony śluzowej w sitowiu po stronie prawej.  Klatka piersiowa i śródpiersie: Masa miękkotkankowa w śródpiersiu przednim i środkowym, pośrodkowo i po stronie prawej, wielkości ok.  89x46x98mm, z obszarami rozpadu, SUV max do 3,4. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zwiększona ilość płynu w worku osierdziowym, o szerokości płaszcza - do 12mm, a nadprzeponowo do 28mm. Obwodowe zmiany włókniste w płacie górnym płuca prawego. Niewielkie zmiany włókniste w segm. 5 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Pobudzenie metaboliczne w układzie kostnym- związane ze stosowanym leczeniem?. Spłycenie fizjologicznych krzywizn kręgosłupa. Dyskopatia na poziomie L5/S1. Os sacrum arcuatum.   Wartości referencyjne: MBPS SUVmax do 1,8; Prawy płat wątroby SUVmax do 3,1.</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Polipowate zgrubienie błony śluzowej w sitowiu po stronie prawej.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Masa miękkotkankowa w śródpiersiu przednim i środkowym, pośrodkowo i po stronie prawej, wielkości ok.  89x46x98mm, z obszarami rozpadu, SUV max do 3,4. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zwiększona ilość płynu w worku osierdziowym, o szerokości płaszcza - do 12mm, a nadprzeponowo do 28mm. Obwodowe zmiany włókniste w płacie górnym płuca prawego. Niewielkie zmiany włókniste w segm. 5 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne w układzie kostnym- związane ze stosowanym leczeniem?. Spłycenie fizjologicznych krzywizn kręgosłupa. Dyskopatia na poziomie L5/S1. Os sacrum arcuatum.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono dobrą odpowiedź metaboliczną i radiologiczną na stosowane leczenie. Masa resztkowa w śródpiersiu - do dalszej kontroli.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>3.4</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 63 min od podania 18F-FDG. Glikemia: 102mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Aktywność metaboliczna w prawym fałdzie nalewkowo-nagłośniowym, SUV max 5,3- do ew. kontroli laryngologicznej.   Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Polipowate zgrubienie błony śluzowej w sitowiu po stronie prawej.  Klatka piersiowa i śródpiersie: Masa miękkotkankowa w śródpiersiu przednim i środkowym, pośrodkowo i po stronie prawej, wielkości ok. 62x29x50mm, z obszarami rozpadu, SUV max do 3,7. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zwiększona ilość płynu w worku osierdziowym, o szerokości płaszcza - do 12 mm nadprzeponowo. Obwodowe zmiany włókniste w płacie górnym płuca prawego. Niewielkie zmiany włókniste w segm. 5 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Pobudzenie metaboliczne w układzie kostnym- związane ze stosowanym leczeniem?. Spłycenie fizjologicznych krzywizn kręgosłupa. Dyskopatia na poziomie L5/S1. Os sacrum arcuatum.   Wartości referencyjne: MBPS SUVmax do 1,6; Prawy płat wątroby SUVmax do 2,5.</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Aktywność metaboliczna w prawym fałdzie nalewkowo-nagłośniowym, SUV max 5,3- do ew. kontroli laryngologicznej.   Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Polipowate zgrubienie błony śluzowej w sitowiu po stronie prawej.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Masa miękkotkankowa w śródpiersiu przednim i środkowym, pośrodkowo i po stronie prawej, wielkości ok. 62x29x50mm, z obszarami rozpadu, SUV max do 3,7. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zwiększona ilość płynu w worku osierdziowym, o szerokości płaszcza - do 12 mm nadprzeponowo. Obwodowe zmiany włókniste w płacie górnym płuca prawego. Niewielkie zmiany włókniste w segm. 5 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne w układzie kostnym- związane ze stosowanym leczeniem?. Spłycenie fizjologicznych krzywizn kręgosłupa. Dyskopatia na poziomie L5/S1. Os sacrum arcuatum.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywność metaboliczną w  prawym fałdzie nalewkowo-nagłośniowym- do ew. kontroli laryngologicznej.    Poza tym jak z badaniu z dnia 28.06.2022 masa resztkowa w śródpiersiu - do dalszej kontroli.   Ponadto jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>5.3</v>
       </c>
     </row>
@@ -568,20 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58min od podania 18F-FDG. Glikemia: 92mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Polipowate zgrubienie błony śluzowej w sitowiu po stronie prawej. Węzeł chłonny przedziału 3 po stronie prawej wielkości 10mm, SUV max 1,5 [IM 80].  Klatka piersiowa i śródpiersie: Masa miękkotkankowa w śródpiersiu przednim i środkowym, pośrodkowo i po stronie prawej, wielkości ok. 58x26x50mm, z hyperdensyjnymi obszarami, głównie nieaktywna metabolicznie, z wartościami SUV max do 2,5 (w okolicach zmian hyperdensyjnych). Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zwiększona ilość płynu w worku osierdziowym, o szerokości płaszcza - do 11mm. Obwodowe zmiany włókniste w płacie górnym płuca prawego. Drobne zmiany włókniste w segm. 5 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Pobudzenie metaboliczne w układzie kostnym- związane ze stosowanym leczeniem?. Spłycenie fizjologicznych krzywizn kręgosłupa. Łukowato kyfotyczne ustawienie kręgosłupa szyjnego. Niewielka prawowypukła skolioza kręgosłupa piersiowego, z rotacją kręgów. Dyskopatia na poziomie L5/S1. Os sacrum arcuatum. Ok. 4mm wyspy kostne w lewej kości kulszowej i w głowie lewej kości udowej. Drobne obwodowe torbielki i wyspa kostna w głowie prawej kosci udowej.  Inne: Miejednoznaczne mierne pobudzenie metaboliczne w mięśniu czworobocznym lędźwi po stronie lewej, SUV max 2,2 - do kontroli.    Wartości referencyjne: MBPS SUVmax do 1,2 Prawy płat wątroby SUVmax do 2,2.</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Polipowate zgrubienie błony śluzowej w sitowiu po stronie prawej. Węzeł chłonny przedziału 3 po stronie prawej wielkości 10mm, SUV max 1,5 [IM 80].</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Masa miękkotkankowa w śródpiersiu przednim i środkowym, pośrodkowo i po stronie prawej, wielkości ok. 58x26x50mm, z hyperdensyjnymi obszarami, głównie nieaktywna metabolicznie, z wartościami SUV max do 2,5 (w okolicach zmian hyperdensyjnych). Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zwiększona ilość płynu w worku osierdziowym, o szerokości płaszcza - do 11mm. Obwodowe zmiany włókniste w płacie górnym płuca prawego. Drobne zmiany włókniste w segm. 5 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne w układzie kostnym- związane ze stosowanym leczeniem?. Spłycenie fizjologicznych krzywizn kręgosłupa. Łukowato kyfotyczne ustawienie kręgosłupa szyjnego. Niewielka prawowypukła skolioza kręgosłupa piersiowego, z rotacją kręgów. Dyskopatia na poziomie L5/S1. Os sacrum arcuatum. Ok. 4mm wyspy kostne w lewej kości kulszowej i w głowie lewej kości udowej. Drobne obwodowe torbielki i wyspa kostna w głowie prawej kosci udowej.  Inne: Miejednoznaczne mierne pobudzenie metaboliczne w mięśniu czworobocznym lędźwi po stronie lewej, SUV max 2,2 - do kontroli.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność masy resztkowej w śródpiersiu, głównie nieaktywnej metabolicznie, ogniskowo miernie pobudzonej metabolicznie (w okolicach zmian hyperdensyjnych)- do dalszej kontroli.   Ponadto jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="L5" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -601,20 +726,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57min od podania 18F-FDG. Glikemia: 106mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Polipowate zgrubienie błony śluzowej w sitowiu po stronie prawej.   Klatka piersiowa i śródpiersie: Masa miękkotkankowa w śródpiersiu przednim i środkowym, pośrodkowo i po stronie prawej, wielkości ok. 46x13x41mm, z hyperdensyjnymi obszarami, głównie nieaktywna metabolicznie, z wartościami SUV max do 2,9 (w okolicach zmian hyperdensyjnych). Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zwiększona ilość płynu w worku osierdziowym, o szerokości płaszcza - do 11mm nadprzeponowo. Obwodowe zmiany włókniste w płacie górnym płuca prawego. Drobne zmiany włókniste w segm. 5 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Pobudzenie metaboliczne w układzie kostnym- związane ze stosowanym leczeniem?. Spłycenie fizjologicznych krzywizn kręgosłupa. Łukowato kyfotyczne ustawienie kręgosłupa szyjnego. Niewielka prawowypukła skolioza kręgosłupa piersiowego, z rotacją kręgów. Dyskopatia na poziomie L5/S1. Os sacrum arcuatum. Ok. 4mm wyspy kostne w lewej kości kulszowej i w głowie lewej kości udowej. Drobne obwodowe torbielki i wyspa kostna w głowie prawej kości udowej.  Inne: Zwiększony metabolizm FDG w tkance brunatnej szyi i KLP.   Wartości referencyjne: MBPS SUVmax do 1,8 Prawy płat wątroby SUVmax do 2,9.</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Polipowate zgrubienie błony śluzowej w sitowiu po stronie prawej.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Masa miękkotkankowa w śródpiersiu przednim i środkowym, pośrodkowo i po stronie prawej, wielkości ok. 46x13x41mm, z hyperdensyjnymi obszarami, głównie nieaktywna metabolicznie, z wartościami SUV max do 2,9 (w okolicach zmian hyperdensyjnych). Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Zwiększona ilość płynu w worku osierdziowym, o szerokości płaszcza - do 11mm nadprzeponowo. Obwodowe zmiany włókniste w płacie górnym płuca prawego. Drobne zmiany włókniste w segm. 5 płuca prawego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne w układzie kostnym- związane ze stosowanym leczeniem?. Spłycenie fizjologicznych krzywizn kręgosłupa. Łukowato kyfotyczne ustawienie kręgosłupa szyjnego. Niewielka prawowypukła skolioza kręgosłupa piersiowego, z rotacją kręgów. Dyskopatia na poziomie L5/S1. Os sacrum arcuatum. Ok. 4mm wyspy kostne w lewej kości kulszowej i w głowie lewej kości udowej. Drobne obwodowe torbielki i wyspa kostna w głowie prawej kości udowej.  Inne: Zwiększony metabolizm FDG w tkance brunatnej szyi i KLP.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono jak w badaniu poprzednim obecność masy resztkowej w śródpiersiu, głównie nieaktywnej metabolicznie, ogniskowo miernie pobudzonej metabolicznie (w okolicach zmian hyperdensyjnych)- do dalszej kontroli.   Ponadto jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="L6" t="n">
         <v>2.9</v>
       </c>
     </row>
